--- a/fvsOL/inst/extdata/databaseDescription.xlsx
+++ b/fvsOL/inst/extdata/databaseDescription.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code_repos\ForestVegetationSimulator-Interface\fvsOL\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49260AB9-E69F-465B-9797-47A428FD5CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB5B6F4-0B6F-4980-AD16-EF23BB9506D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="718" firstSheet="17" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ColorKey" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10866" uniqueCount="3165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10870" uniqueCount="3167">
   <si>
     <t>Tab Color</t>
   </si>
@@ -9650,6 +9650,12 @@
   </si>
   <si>
     <t>TPrdTpa</t>
+  </si>
+  <si>
+    <t>LocationCode</t>
+  </si>
+  <si>
+    <t>Forest Location Code</t>
   </si>
 </sst>
 </file>
@@ -38670,7 +38676,7 @@
   <sheetPr>
     <tabColor rgb="FF203864"/>
   </sheetPr>
-  <dimension ref="A1:AMI34"/>
+  <dimension ref="A1:AMI35"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" style="22" customWidth="1"/>
@@ -38724,292 +38730,300 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="52" t="s">
-        <v>2984</v>
+        <v>3165</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>2901</v>
+        <v>2221</v>
       </c>
       <c r="C4" s="52" t="s">
         <v>189</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>3032</v>
+        <v>3166</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>521</v>
+        <v>2984</v>
       </c>
       <c r="B5" s="52" t="s">
-        <v>522</v>
+        <v>2901</v>
       </c>
       <c r="C5" s="52" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="52" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>2985</v>
+        <v>522</v>
       </c>
       <c r="C6" s="52" t="s">
         <v>155</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B7" s="52" t="s">
-        <v>528</v>
+        <v>2985</v>
       </c>
       <c r="C7" s="52" t="s">
         <v>155</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="52" t="s">
+        <v>527</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>528</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>3035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="52" t="s">
         <v>2987</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B9" s="52" t="s">
         <v>2986</v>
       </c>
-      <c r="C8" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="52" t="s">
+      <c r="C9" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>3036</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="52" t="s">
+    <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="52" t="s">
         <v>3108</v>
       </c>
-      <c r="B9" s="52" t="s">
+      <c r="B10" s="52" t="s">
         <v>3109</v>
       </c>
-      <c r="C9" s="52" t="s">
+      <c r="C10" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D10" s="52" t="s">
         <v>3145</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="52" t="s">
-        <v>2988</v>
-      </c>
-      <c r="B10" s="52" t="s">
-        <v>2989</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="52" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
       <c r="B11" s="52" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="C11" s="52" t="s">
         <v>189</v>
       </c>
       <c r="D11" s="52" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="52" t="s">
+        <v>2990</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="52" t="s">
         <v>3038</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="52" t="s">
+    <row r="13" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A13" s="52" t="s">
         <v>3103</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B13" s="52" t="s">
         <v>3104</v>
-      </c>
-      <c r="C12" s="52" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>3105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="52" t="s">
-        <v>2992</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>2993</v>
       </c>
       <c r="C13" s="52" t="s">
         <v>155</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>3039</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="52" t="s">
-        <v>2994</v>
+        <v>2992</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>2995</v>
+        <v>2993</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>2996</v>
+        <v>2994</v>
       </c>
       <c r="B15" s="52" t="s">
-        <v>2997</v>
+        <v>2995</v>
       </c>
       <c r="C15" s="52" t="s">
         <v>174</v>
       </c>
       <c r="D15" s="52" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="52" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="52" t="s">
         <v>2998</v>
       </c>
-      <c r="B16" s="52" t="s">
+      <c r="B17" s="52" t="s">
         <v>2999</v>
       </c>
-      <c r="C16" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D16" s="52" t="s">
+      <c r="C17" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D17" s="52" t="s">
         <v>3042</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="52" t="s">
-        <v>3022</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>3000</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="52" t="s">
+        <v>3022</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>3043</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="52" t="s">
         <v>3023</v>
       </c>
-      <c r="B18" s="52" t="s">
+      <c r="B19" s="52" t="s">
         <v>3001</v>
       </c>
-      <c r="C18" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="52" t="s">
+      <c r="C19" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="52" t="s">
         <v>3044</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="52" t="s">
-        <v>3024</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>3002</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D19" s="52" t="s">
-        <v>3045</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="52" t="s">
+        <v>3024</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>3045</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="52" t="s">
         <v>3003</v>
       </c>
-      <c r="B20" s="52" t="s">
+      <c r="B21" s="52" t="s">
         <v>3004</v>
       </c>
-      <c r="C20" s="52" t="s">
+      <c r="C21" s="52" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D21" s="52" t="s">
         <v>3046</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="52" t="s">
-        <v>3005</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>3006</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D21" s="52" t="s">
-        <v>3047</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>3006</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>3047</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="52" t="s">
         <v>3007</v>
       </c>
-      <c r="B22" s="52" t="s">
+      <c r="B23" s="52" t="s">
         <v>3008</v>
       </c>
-      <c r="C22" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="52" t="s">
+      <c r="C23" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="52" t="s">
         <v>3048</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="52" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="52" t="s">
         <v>3009</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B24" s="52" t="s">
         <v>3010</v>
       </c>
-      <c r="C23" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="D23" s="52" t="s">
+      <c r="C24" s="52" t="s">
+        <v>174</v>
+      </c>
+      <c r="D24" s="52" t="s">
         <v>3049</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G24" s="22" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="52"/>
@@ -39070,6 +39084,12 @@
       <c r="B34" s="52"/>
       <c r="C34" s="52"/>
       <c r="D34" s="52"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
